--- a/data/trans_camb/IP1001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,12</t>
+          <t>-0,63; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,12</t>
+          <t>-1,9; 3,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,51</t>
+          <t>-2,31; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,3</t>
+          <t>-1,28; 3,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,1</t>
+          <t>-0,91; 3,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,96</t>
+          <t>-1,2; 2,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,81</t>
+          <t>-0,17; 3,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,92</t>
+          <t>-0,85; 2,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,22</t>
+          <t>-1,3; 2,29</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,03; 1039,68</t>
+          <t>-49,74; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 725,65</t>
+          <t>-25,08; 774,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 567,36</t>
+          <t>-56,98; 573,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 455,41</t>
+          <t>-70,98; 465,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,17</t>
+          <t>-3,2; 1,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,24</t>
+          <t>-1,09; 4,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,6</t>
+          <t>-2,48; 2,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,72</t>
+          <t>-2,35; 2,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,77</t>
+          <t>-2,08; 2,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,84</t>
+          <t>-1,09; 4,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,26</t>
+          <t>-2,02; 1,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,9</t>
+          <t>-1,04; 2,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,0</t>
+          <t>-1,1; 2,92</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 107,39</t>
+          <t>-86,26; 109,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 305,31</t>
+          <t>-36,24; 311,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 215,17</t>
+          <t>-71,09; 223,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,0; 188,79</t>
+          <t>-63,76; 175,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 182,73</t>
+          <t>-55,86; 201,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 302,08</t>
+          <t>-32,61; 292,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,38; 72,27</t>
+          <t>-61,34; 69,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 173,64</t>
+          <t>-32,61; 144,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 150,08</t>
+          <t>-32,07; 154,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -0,86</t>
+          <t>-6,83; -0,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -1,34</t>
+          <t>-7,45; -1,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 0,71</t>
+          <t>-6,09; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,45</t>
+          <t>-2,64; 1,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,35</t>
+          <t>-2,39; 2,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 11,2</t>
+          <t>-0,77; 9,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,11</t>
+          <t>-4,0; -0,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,15</t>
+          <t>-3,85; 0,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 3,54</t>
+          <t>-2,26; 3,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,79; 2,0</t>
+          <t>-94,97; -14,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,57</t>
+          <t>-100,0; -20,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,44; 34,03</t>
+          <t>-88,22; 36,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-87,17; 235,77</t>
+          <t>-86,93; 245,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,96; 276,35</t>
+          <t>-82,5; 318,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 957,93</t>
+          <t>-47,53; 1590,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,2; 6,61</t>
+          <t>-87,55; -2,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,93; 21,01</t>
+          <t>-83,21; 26,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 175,14</t>
+          <t>-57,57; 161,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 0,41</t>
+          <t>-4,82; 0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,6</t>
+          <t>-4,91; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,77</t>
+          <t>-4,54; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,94</t>
+          <t>-3,43; 3,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,47</t>
+          <t>-4,1; 1,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,42</t>
+          <t>-4,76; 1,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,87</t>
+          <t>-3,51; 1,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,22</t>
+          <t>-3,72; 0,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,41</t>
+          <t>-3,69; 0,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,86; 52,19</t>
+          <t>-91,25; 52,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 64,57</t>
+          <t>-91,47; 50,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,55; 92,18</t>
+          <t>-89,6; 110,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,51; 119,23</t>
+          <t>-62,08; 130,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 63,6</t>
+          <t>-71,18; 81,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,73; 68,75</t>
+          <t>-81,57; 82,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-63,47; 34,47</t>
+          <t>-67,12; 39,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-72,01; 10,64</t>
+          <t>-75,1; 17,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,89; 20,65</t>
+          <t>-74,63; 22,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,22</t>
+          <t>-2,44; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,61</t>
+          <t>-2,23; 0,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,65</t>
+          <t>-2,14; 0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,36</t>
+          <t>-1,23; 1,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,29</t>
+          <t>-1,51; 1,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,85</t>
+          <t>-0,7; 2,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,53</t>
+          <t>-1,5; 0,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,59</t>
+          <t>-1,44; 0,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,32</t>
+          <t>-1,02; 1,23</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 12,02</t>
+          <t>-63,4; 12,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,05; 29,17</t>
+          <t>-58,09; 36,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 33,31</t>
+          <t>-59,0; 30,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 67,42</t>
+          <t>-37,85; 68,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 64,61</t>
+          <t>-43,53; 59,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 135,14</t>
+          <t>-25,29; 127,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 20,53</t>
+          <t>-43,62; 18,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 26,0</t>
+          <t>-42,82; 19,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 56,22</t>
+          <t>-32,11; 49,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,02</t>
+          <t>-0,72; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,95</t>
+          <t>-1,84; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,5</t>
+          <t>-2,1; 3,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,19</t>
+          <t>-0,94; 3,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,81</t>
+          <t>-0,88; 3,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,81</t>
+          <t>-1,27; 3,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,8</t>
+          <t>-0,19; 3,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,91</t>
+          <t>-0,87; 2,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,29</t>
+          <t>-1,13; 2,51</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,74; —</t>
+          <t>-62,75; 1358,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 774,93</t>
+          <t>-29,88; 785,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 573,83</t>
+          <t>-51,32; 637,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,98; 465,2</t>
+          <t>-65,9; 483,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,14</t>
+          <t>-3,18; 1,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,38</t>
+          <t>-1,27; 4,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,92</t>
+          <t>-2,6; 2,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,71</t>
+          <t>-2,36; 2,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,93</t>
+          <t>-2,3; 2,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,96</t>
+          <t>-1,08; 5,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,31</t>
+          <t>-2,27; 1,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,67</t>
+          <t>-1,13; 2,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,92</t>
+          <t>-1,15; 3,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,26; 109,68</t>
+          <t>-81,67; 129,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 311,24</t>
+          <t>-40,45; 320,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 223,03</t>
+          <t>-76,18; 213,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,76; 175,22</t>
+          <t>-63,71; 176,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 201,92</t>
+          <t>-62,92; 177,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 292,82</t>
+          <t>-34,02; 348,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,34; 69,02</t>
+          <t>-64,83; 62,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 144,43</t>
+          <t>-32,94; 151,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 154,19</t>
+          <t>-34,33; 167,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,89</t>
+          <t>-6,77; -0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -1,35</t>
+          <t>-7,16; -1,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 0,77</t>
+          <t>-6,11; 0,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,73</t>
+          <t>-2,71; 1,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,42</t>
+          <t>-2,26; 2,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 9,05</t>
+          <t>-0,81; 9,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -0,2</t>
+          <t>-3,76; -0,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,25</t>
+          <t>-3,8; -0,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,56</t>
+          <t>-2,21; 3,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,97; -14,17</t>
+          <t>-97,44; 0,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,46</t>
+          <t>-100,0; -19,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,22; 36,13</t>
+          <t>-88,14; 29,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,93; 245,5</t>
+          <t>-90,92; 316,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,5; 318,73</t>
+          <t>-76,88; 371,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 1590,22</t>
+          <t>-61,25; 1051,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,55; -2,42</t>
+          <t>-86,75; 5,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,21; 26,43</t>
+          <t>-83,42; 6,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,57; 161,73</t>
+          <t>-56,08; 167,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,49</t>
+          <t>-4,5; 0,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,41</t>
+          <t>-4,71; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,97</t>
+          <t>-4,54; 0,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,25</t>
+          <t>-3,53; 3,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,81</t>
+          <t>-4,23; 1,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,32</t>
+          <t>-4,69; 1,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,06</t>
+          <t>-3,24; 0,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,37</t>
+          <t>-3,79; 0,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,43</t>
+          <t>-3,83; 0,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-91,25; 52,49</t>
+          <t>-90,32; 41,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,47; 50,34</t>
+          <t>-91,48; 63,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,6; 110,49</t>
+          <t>-90,57; 65,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 130,25</t>
+          <t>-59,23; 126,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 81,51</t>
+          <t>-72,76; 73,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,57; 82,58</t>
+          <t>-79,0; 70,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 39,22</t>
+          <t>-64,67; 37,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,1; 17,18</t>
+          <t>-73,74; 14,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 22,07</t>
+          <t>-77,0; 23,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,23</t>
+          <t>-2,57; 0,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,7</t>
+          <t>-2,17; 0,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,59</t>
+          <t>-2,24; 0,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,38</t>
+          <t>-1,28; 1,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,2</t>
+          <t>-1,4; 1,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,68</t>
+          <t>-0,54; 2,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,42</t>
+          <t>-1,51; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,48</t>
+          <t>-1,33; 0,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,23</t>
+          <t>-0,97; 1,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 12,87</t>
+          <t>-67,68; 12,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 36,04</t>
+          <t>-56,88; 24,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 30,14</t>
+          <t>-60,09; 20,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 68,7</t>
+          <t>-39,36; 68,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 59,2</t>
+          <t>-43,08; 65,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 127,23</t>
+          <t>-18,25; 140,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 18,5</t>
+          <t>-44,83; 20,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 19,93</t>
+          <t>-39,6; 24,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 49,66</t>
+          <t>-29,83; 55,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,72</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,66</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,66</t>
+          <t>-0,96; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,25</t>
+          <t>-0,73; 4,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,73</t>
+          <t>-1,05; 3,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,12</t>
+          <t>-0,96; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,67</t>
+          <t>-1,79; 4,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,0</t>
+          <t>-2,08; 3,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,84</t>
+          <t>-0,07; 3,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,87</t>
+          <t>-0,63; 2,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,51</t>
+          <t>-1,01; 2,39</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>94,99%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>153,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>45,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>121,71%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,75; 1358,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-59,03; 1039,68</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 785,31</t>
+          <t>-22,36; 725,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 637,25</t>
+          <t>-52,4; 567,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,9; 483,91</t>
+          <t>-65,43; 489,29</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,49</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,08</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-0,43</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,23</t>
+          <t>-2,48; 2,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,41</t>
+          <t>-2,35; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,72</t>
+          <t>-1,01; 4,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,79</t>
+          <t>-3,21; 1,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,85</t>
+          <t>-1,4; 4,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 5,21</t>
+          <t>-2,56; 2,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,18</t>
+          <t>-2,1; 1,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,73</t>
+          <t>-0,9; 2,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,05</t>
+          <t>-0,95; 3,2</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61,6%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-38,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>58,83%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,88%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,67; 129,15</t>
+          <t>-61,0; 188,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 320,53</t>
+          <t>-60,39; 182,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 213,72</t>
+          <t>-31,03; 305,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 176,79</t>
+          <t>-83,08; 107,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 177,38</t>
+          <t>-39,28; 305,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 348,76</t>
+          <t>-74,96; 241,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,83; 62,73</t>
+          <t>-59,38; 72,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 151,45</t>
+          <t>-26,48; 173,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 167,2</t>
+          <t>-30,93; 157,69</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,76</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,34</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,47</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -1109,32 +1109,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -0,76</t>
+          <t>-2,76; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -1,25</t>
+          <t>-2,15; 2,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,59</t>
+          <t>-1,27; 5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,65</t>
+          <t>-6,73; -0,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,37</t>
+          <t>-7,43; -1,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,17</t>
+          <t>-5,26; 1,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -0,12</t>
+          <t>-3,61; 0,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,61</t>
+          <t>-2,33; 2,54</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-24,04%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78,23%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-75,39%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-81,61%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-50,78%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-24,04%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>134,19%</t>
+          <t>-38,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>-1,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-97,44; 0,38</t>
+          <t>-87,17; 235,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,87</t>
+          <t>-82,96; 276,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,14; 29,53</t>
+          <t>-62,58; 586,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 316,88</t>
+          <t>-94,79; 2,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 371,75</t>
+          <t>-100,0; -8,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,25; 1051,12</t>
+          <t>-82,08; 65,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,75; 5,43</t>
+          <t>-85,2; 6,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 6,97</t>
+          <t>-83,93; 21,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 167,5</t>
+          <t>-56,24; 112,51</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,94</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,91</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,44</t>
+          <t>-3,43; 2,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,68</t>
+          <t>-4,49; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,83</t>
+          <t>-4,79; 1,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,18</t>
+          <t>-4,74; 0,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,65</t>
+          <t>-4,52; 0,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,63</t>
+          <t>-4,44; 0,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,91</t>
+          <t>-3,15; 0,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,27</t>
+          <t>-3,61; 0,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,53</t>
+          <t>-3,75; 0,49</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-6,17%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-33,23%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-35,68%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-57,95%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-56,89%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-48,52%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-6,17%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-33,23%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-37,75%</t>
+          <t>-48,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,92%</t>
+          <t>-41,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,32; 41,86</t>
+          <t>-57,51; 119,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,48; 63,87</t>
+          <t>-76,0; 63,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,57; 65,21</t>
+          <t>-79,89; 73,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 126,44</t>
+          <t>-90,86; 52,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,76; 73,77</t>
+          <t>-89,67; 64,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 70,57</t>
+          <t>-89,44; 93,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 37,88</t>
+          <t>-63,47; 34,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,74; 14,24</t>
+          <t>-72,01; 10,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 23,55</t>
+          <t>-73,71; 22,26</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,78</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,19</t>
+          <t>-1,37; 1,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,51</t>
+          <t>-1,42; 1,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,45</t>
+          <t>-0,81; 2,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,37</t>
+          <t>-2,49; 0,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,27</t>
+          <t>-2,14; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,94</t>
+          <t>-2,23; 0,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,45</t>
+          <t>-1,51; 0,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,56</t>
+          <t>-1,46; 0,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,28</t>
+          <t>-1,01; 1,17</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-3,09%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-36,91%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-25,79%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-29,74%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-3,09%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>-23,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 12,23</t>
+          <t>-40,66; 67,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 24,42</t>
+          <t>-44,02; 64,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 20,88</t>
+          <t>-25,31; 110,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 68,5</t>
+          <t>-66,07; 12,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 65,68</t>
+          <t>-58,05; 29,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 140,99</t>
+          <t>-58,9; 43,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 20,45</t>
+          <t>-44,99; 20,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 24,37</t>
+          <t>-43,15; 26,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 55,89</t>
+          <t>-32,25; 52,22</t>
         </is>
       </c>
     </row>
